--- a/data/2.b_Hybrider_Netzzugang_2025_5%/Power_Parameters.xlsx
+++ b/data/2.b_Hybrider_Netzzugang_2025_5%/Power_Parameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr codeName="DieseArbeitsmappe" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\2.b_Hybrider_Netzzugang\1_Model\2.b_Hybrider_Netzzugang_2025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\LEGO-Pyomo\data\2.b_Hybrider_Netzzugang_2035_5%\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{721F61BD-8B75-4FAF-8747-1EB91C9F602E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDED682B-B4F5-4A6F-97AF-59C5209C152F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36490" yWindow="3860" windowWidth="28490" windowHeight="15240" tabRatio="958" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="958" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Power Parameters" sheetId="121" r:id="rId1"/>
@@ -58,6 +58,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -1208,25 +1211,25 @@
     <tabColor rgb="FF008080"/>
   </sheetPr>
   <dimension ref="B1:H98"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.86328125" defaultRowHeight="18.75" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.8984375" defaultRowHeight="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.3984375" style="1" customWidth="1"/>
     <col min="2" max="2" width="51" style="1" customWidth="1"/>
-    <col min="3" max="3" width="30.86328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.86328125" style="1"/>
+    <col min="3" max="3" width="30.8984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.8984375" style="1"/>
     <col min="5" max="5" width="21" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="139.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="139.69921875" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.265625" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="10.86328125" style="1"/>
+    <col min="8" max="8" width="14.296875" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.8984375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:8" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="2:8" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:8" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="7" t="s">
         <v>13</v>
       </c>
@@ -1246,7 +1249,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="2:8" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:8" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="5" t="s">
         <v>33</v>
       </c>
@@ -1254,7 +1257,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="2:8" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:8" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>34</v>
       </c>
@@ -1262,8 +1265,8 @@
         <v>95</v>
       </c>
     </row>
-    <row r="6" spans="2:8" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="7" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:8" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="7" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="5" t="s">
         <v>14</v>
       </c>
@@ -1271,7 +1274,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
         <v>2</v>
       </c>
@@ -1288,8 +1291,8 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="2:8" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="10" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:8" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="5" t="s">
         <v>15</v>
       </c>
@@ -1297,7 +1300,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
         <v>3</v>
       </c>
@@ -1314,12 +1317,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="2:8" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:8" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
     </row>
-    <row r="13" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="5" t="s">
         <v>16</v>
       </c>
@@ -1327,7 +1330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
         <v>27</v>
       </c>
@@ -1344,13 +1347,13 @@
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="3"/>
       <c r="E15"/>
       <c r="F15"/>
       <c r="G15"/>
     </row>
-    <row r="16" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="5" t="s">
         <v>107</v>
       </c>
@@ -1360,7 +1363,7 @@
       <c r="F16"/>
       <c r="G16"/>
     </row>
-    <row r="17" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="3" t="s">
         <v>111</v>
       </c>
@@ -1373,14 +1376,14 @@
       <c r="F17"/>
       <c r="G17"/>
     </row>
-    <row r="18" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="5"/>
       <c r="C18"/>
       <c r="E18"/>
       <c r="F18"/>
       <c r="G18"/>
     </row>
-    <row r="19" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="5" t="s">
         <v>109</v>
       </c>
@@ -1390,7 +1393,7 @@
       <c r="F19"/>
       <c r="G19"/>
     </row>
-    <row r="20" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
         <v>110</v>
       </c>
@@ -1401,12 +1404,12 @@
         <v>108</v>
       </c>
     </row>
-    <row r="21" spans="2:7" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:7" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="7" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="22" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="5" t="s">
         <v>74</v>
       </c>
@@ -1414,7 +1417,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="23" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="3" t="s">
         <v>75</v>
       </c>
@@ -1425,11 +1428,11 @@
         <v>76</v>
       </c>
     </row>
-    <row r="24" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="3"/>
       <c r="C24"/>
     </row>
-    <row r="25" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="5" t="s">
         <v>71</v>
       </c>
@@ -1437,7 +1440,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="3" t="s">
         <v>72</v>
       </c>
@@ -1448,11 +1451,11 @@
         <v>80</v>
       </c>
     </row>
-    <row r="27" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="3"/>
       <c r="C27"/>
     </row>
-    <row r="28" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="5" t="s">
         <v>77</v>
       </c>
@@ -1460,7 +1463,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="3" t="s">
         <v>78</v>
       </c>
@@ -1471,11 +1474,11 @@
         <v>79</v>
       </c>
     </row>
-    <row r="30" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="3"/>
       <c r="C30"/>
     </row>
-    <row r="31" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="5" t="s">
         <v>81</v>
       </c>
@@ -1483,22 +1486,22 @@
         <v>24</v>
       </c>
     </row>
-    <row r="32" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="3" t="s">
         <v>82</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="33" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="3"/>
       <c r="C33"/>
     </row>
-    <row r="34" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="5" t="s">
         <v>56</v>
       </c>
@@ -1506,7 +1509,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="35" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="3" t="s">
         <v>57</v>
       </c>
@@ -1517,11 +1520,11 @@
         <v>84</v>
       </c>
     </row>
-    <row r="36" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
     </row>
-    <row r="37" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="5" t="s">
         <v>94</v>
       </c>
@@ -1529,7 +1532,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="38" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="3" t="s">
         <v>93</v>
       </c>
@@ -1540,10 +1543,10 @@
         <v>94</v>
       </c>
     </row>
-    <row r="39" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="3"/>
     </row>
-    <row r="40" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="5" t="s">
         <v>104</v>
       </c>
@@ -1551,7 +1554,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="41" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="3" t="s">
         <v>105</v>
       </c>
@@ -1562,10 +1565,10 @@
         <v>106</v>
       </c>
     </row>
-    <row r="42" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="3"/>
     </row>
-    <row r="43" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="5" t="s">
         <v>112</v>
       </c>
@@ -1573,7 +1576,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="3" t="s">
         <v>113</v>
       </c>
@@ -1584,15 +1587,15 @@
         <v>112</v>
       </c>
     </row>
-    <row r="45" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="3"/>
     </row>
-    <row r="46" spans="2:6" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:6" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="47" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="5" t="s">
         <v>19</v>
       </c>
@@ -1600,7 +1603,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="48" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="3" t="s">
         <v>29</v>
       </c>
@@ -1611,10 +1614,10 @@
         <v>30</v>
       </c>
     </row>
-    <row r="49" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="3"/>
     </row>
-    <row r="50" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="5" t="s">
         <v>20</v>
       </c>
@@ -1622,7 +1625,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="51" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="3" t="s">
         <v>7</v>
       </c>
@@ -1630,10 +1633,10 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="3"/>
     </row>
-    <row r="53" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="5" t="s">
         <v>96</v>
       </c>
@@ -1641,7 +1644,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="54" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="3" t="s">
         <v>98</v>
       </c>
@@ -1652,10 +1655,10 @@
         <v>99</v>
       </c>
     </row>
-    <row r="55" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="55" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="3"/>
     </row>
-    <row r="56" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="5" t="s">
         <v>21</v>
       </c>
@@ -1663,7 +1666,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="57" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="3" t="s">
         <v>8</v>
       </c>
@@ -1671,10 +1674,10 @@
         <v>60</v>
       </c>
     </row>
-    <row r="58" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="3"/>
     </row>
-    <row r="59" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="5" t="s">
         <v>49</v>
       </c>
@@ -1682,7 +1685,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="60" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="3" t="s">
         <v>50</v>
       </c>
@@ -1690,10 +1693,10 @@
         <v>180</v>
       </c>
     </row>
-    <row r="61" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="3"/>
     </row>
-    <row r="62" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="5" t="s">
         <v>67</v>
       </c>
@@ -1701,7 +1704,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="63" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="3" t="s">
         <v>66</v>
       </c>
@@ -1709,10 +1712,10 @@
         <v>9</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="3"/>
     </row>
-    <row r="65" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B65" s="5" t="s">
         <v>22</v>
       </c>
@@ -1720,7 +1723,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="66" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="3" t="s">
         <v>11</v>
       </c>
@@ -1731,10 +1734,10 @@
         <v>69</v>
       </c>
     </row>
-    <row r="67" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B67" s="3"/>
     </row>
-    <row r="68" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B68" s="5" t="s">
         <v>23</v>
       </c>
@@ -1742,7 +1745,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="3" t="s">
         <v>12</v>
       </c>
@@ -1750,10 +1753,10 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="70" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="3"/>
     </row>
-    <row r="71" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" s="5" t="s">
         <v>101</v>
       </c>
@@ -1761,7 +1764,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="72" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="3" t="s">
         <v>102</v>
       </c>
@@ -1772,12 +1775,12 @@
         <v>103</v>
       </c>
     </row>
-    <row r="73" spans="2:5" s="4" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="2:5" s="4" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="74" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B74" s="5" t="s">
         <v>32</v>
       </c>
@@ -1785,7 +1788,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="75" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="3" t="s">
         <v>25</v>
       </c>
@@ -1793,7 +1796,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="77" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="5" t="s">
         <v>53</v>
       </c>
@@ -1801,7 +1804,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="78" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B78" s="3" t="s">
         <v>54</v>
       </c>
@@ -1812,12 +1815,12 @@
         <v>55</v>
       </c>
     </row>
-    <row r="80" spans="2:5" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="2:5" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B80" s="7" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="81" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B81" s="5" t="s">
         <v>17</v>
       </c>
@@ -1825,7 +1828,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B82" s="3" t="s">
         <v>6</v>
       </c>
@@ -1842,11 +1845,11 @@
         <v>47</v>
       </c>
     </row>
-    <row r="83" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B83" s="3"/>
       <c r="C83"/>
     </row>
-    <row r="84" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" s="5" t="s">
         <v>36</v>
       </c>
@@ -1854,7 +1857,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B85" s="3" t="s">
         <v>65</v>
       </c>
@@ -1871,11 +1874,11 @@
         <v>47</v>
       </c>
     </row>
-    <row r="86" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B86" s="3"/>
       <c r="C86"/>
     </row>
-    <row r="87" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B87" s="5" t="s">
         <v>59</v>
       </c>
@@ -1883,7 +1886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B88" s="3" t="s">
         <v>60</v>
       </c>
@@ -1900,11 +1903,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B89" s="3"/>
       <c r="C89"/>
     </row>
-    <row r="90" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B90" s="5" t="s">
         <v>36</v>
       </c>
@@ -1912,7 +1915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B91" s="3" t="s">
         <v>62</v>
       </c>
@@ -1929,16 +1932,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B92" s="3"/>
       <c r="C92"/>
     </row>
-    <row r="93" spans="2:7" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="2:7" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B93" s="7" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="94" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B94" s="5" t="s">
         <v>90</v>
       </c>
@@ -1946,7 +1949,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="95" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B95" s="3" t="s">
         <v>86</v>
       </c>
@@ -1960,7 +1963,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="97" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B97" s="5" t="s">
         <v>89</v>
       </c>
@@ -1968,7 +1971,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="98" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B98" s="3" t="s">
         <v>88</v>
       </c>
@@ -2151,6 +2154,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101004934E3CB1C58BA43BC6E229E2BF20201" ma:contentTypeVersion="4" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="e33ccc94e63df24f58cb47229b46e190">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="87003a75-b64f-4b22-bf19-aa30740e3d46" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0f0f7a5bb162b669de9ce8ff8278c29f" ns2:_="">
     <xsd:import namespace="87003a75-b64f-4b22-bf19-aa30740e3d46"/>
@@ -2296,12 +2305,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -2312,6 +2315,22 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0155F7A0-74CD-4575-8C0B-A34C113F80FE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="87003a75-b64f-4b22-bf19-aa30740e3d46"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{773946F7-566C-458F-95C9-79B0CCE20E87}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2329,22 +2348,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0155F7A0-74CD-4575-8C0B-A34C113F80FE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="87003a75-b64f-4b22-bf19-aa30740e3d46"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13778B2C-CE05-4B32-8196-2F381FEAC95A}">
   <ds:schemaRefs>
